--- a/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Mapping Métier/CDA/FHIR : "Historique de la grossesse"</t>
+    <t>Mapping Métier/CDA/FHIR : "Historique de la grossesse "</t>
   </si>
   <si>
     <t>Status</t>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMHistoriqueGrossesse vers le profil CDA FRCDAHistoriqueDeLaGrossesse, puis vers le profil FHIR FRPregnancyHistoryDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMPregnancyHistory vers le profil CDA FRCDAHistoriqueDeLaGrossesse, puis vers le profil FHIR FRPregnancyHistoryDocument.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-historique-grossesse</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-pregnancy-history</t>
   </si>
   <si>
     <t/>
@@ -109,7 +109,7 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-historique-de-la-grossesse</t>
   </si>
   <si>
-    <t>FRLMHistoriqueGrossesse</t>
+    <t>FRLMPregnancyHistory</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -118,36 +118,33 @@
     <t>FRCDAHistoriqueDeLaGrossesse</t>
   </si>
   <si>
-    <t>FRLMHistoriqueGrossesse.identifiant</t>
-  </si>
-  <si>
-    <t>FRCDAHistoriqueDeLaGrossesse.id</t>
-  </si>
-  <si>
-    <t>FRLMHistoriqueGrossesse.code</t>
+    <t>FRLMPregnancyHistory.header.status</t>
+  </si>
+  <si>
+    <t>FRCDAHistoriqueDeLaGrossesse.statusCode</t>
+  </si>
+  <si>
+    <t>FRLMPregnancyHistory.type</t>
   </si>
   <si>
     <t>FRCDAHistoriqueDeLaGrossesse.code</t>
   </si>
   <si>
-    <t>FRLMHistoriqueGrossesse.statut</t>
-  </si>
-  <si>
-    <t>FRCDAHistoriqueDeLaGrossesse.statusCode</t>
-  </si>
-  <si>
-    <t>FRLMHistoriqueGrossesse.periodeGrossesse</t>
+    <t>FRLMPregnancyHistory.observationDate[x]</t>
   </si>
   <si>
     <t>FRCDAHistoriqueDeLaGrossesse.effectiveTime</t>
   </si>
   <si>
-    <t>FRLMHistoriqueGrossesse.choice[x]</t>
+    <t>FRLMPregnancyHistory.result</t>
   </si>
   <si>
     <t>FRCDAHistoriqueDeLaGrossesse.entryRelationship:frObservationSurLaGrossesse</t>
   </si>
   <si>
+    <t>FRLMPregnancyHistory.component</t>
+  </si>
+  <si>
     <t>FRCDAHistoriqueDeLaGrossesse.entryRelationship:frNaissance</t>
   </si>
   <si>
@@ -157,19 +154,22 @@
     <t>FRPregnancyHistoryDocument</t>
   </si>
   <si>
+    <t>FRLMPregnancyHistory.header.identifier</t>
+  </si>
+  <si>
     <t>FRPregnancyHistoryDocument.identifier</t>
   </si>
   <si>
     <t>FRPregnancyHistoryDocument.code</t>
   </si>
   <si>
-    <t>FRPregnancyHistoryDocument.date</t>
-  </si>
-  <si>
-    <t>FRPregnancyHistoryDocument.entry.item:FRObservationPregnancyDocument</t>
-  </si>
-  <si>
-    <t>FRPregnancyHistoryDocument.entry.item:FRObservationBirthEventDocument</t>
+    <t>FRPregnancyHistoryDocument.effective[x]</t>
+  </si>
+  <si>
+    <t>FRPregnancyHistoryDocument.hasMember:FRObservationPregnancyDocument</t>
+  </si>
+  <si>
+    <t>FRPregnancyHistoryDocument.component</t>
   </si>
 </sst>
 </file>
@@ -421,7 +421,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -535,19 +535,6 @@
         <v>43</v>
       </c>
       <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="E9" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -578,7 +565,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -587,7 +574,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -595,20 +582,20 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -621,7 +608,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -634,7 +621,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -647,7 +634,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
@@ -660,7 +647,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">

--- a/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="70">
   <si>
     <t>Property</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Mapping Métier/CDA/FHIR : "Historique de la grossesse "</t>
+    <t>Mapping Métier/CDA/FHIR : "Historique de la grossesse"</t>
   </si>
   <si>
     <t>Status</t>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMPregnancyHistory vers le profil CDA FRCDAHistoriqueDeLaGrossesse, puis vers le profil FHIR FRPregnancyHistoryDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMPregnancyHistory vers le profil CDA FRCDAHistoriqueDeLaGrossesse, puis vers le profil FHIR FRObservationPregnancyHistoryDocument.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-pregnancy-history</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-pregnancy-history|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-historique-de-la-grossesse</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-historique-de-la-grossesse|0.1.0</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory</t>
@@ -115,61 +115,115 @@
     <t>equivalent</t>
   </si>
   <si>
-    <t>FRCDAHistoriqueDeLaGrossesse</t>
+    <t>Organizer</t>
+  </si>
+  <si>
+    <t>FRLMPregnancyHistory.header.identifier</t>
+  </si>
+  <si>
+    <t>Organizer.id</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.header.status</t>
   </si>
   <si>
-    <t>FRCDAHistoriqueDeLaGrossesse.statusCode</t>
+    <t>Organizer.statusCode</t>
+  </si>
+  <si>
+    <t>FRLMPregnancyHistory.directSubject[x]</t>
+  </si>
+  <si>
+    <t>Organizer.subject</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.type</t>
   </si>
   <si>
-    <t>FRCDAHistoriqueDeLaGrossesse.code</t>
+    <t>Organizer.code</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.observationDate[x]</t>
   </si>
   <si>
-    <t>FRCDAHistoriqueDeLaGrossesse.effectiveTime</t>
+    <t>Organizer.effectiveTime</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.result</t>
   </si>
   <si>
-    <t>FRCDAHistoriqueDeLaGrossesse.entryRelationship:frObservationSurLaGrossesse</t>
+    <t>Organizer.component:frObservationSurLaGrossesse</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.component</t>
   </si>
   <si>
-    <t>FRCDAHistoriqueDeLaGrossesse.entryRelationship:frNaissance</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-pregnancy-history-document</t>
-  </si>
-  <si>
-    <t>FRPregnancyHistoryDocument</t>
-  </si>
-  <si>
-    <t>FRLMPregnancyHistory.header.identifier</t>
-  </si>
-  <si>
-    <t>FRPregnancyHistoryDocument.identifier</t>
-  </si>
-  <si>
-    <t>FRPregnancyHistoryDocument.code</t>
-  </si>
-  <si>
-    <t>FRPregnancyHistoryDocument.effective[x]</t>
-  </si>
-  <si>
-    <t>FRPregnancyHistoryDocument.hasMember:FRObservationPregnancyDocument</t>
-  </si>
-  <si>
-    <t>FRPregnancyHistoryDocument.component</t>
+    <t>Organizer.component:frNaissance</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-pregnancy-history-document|0.1.0</t>
+  </si>
+  <si>
+    <t>Observation</t>
+  </si>
+  <si>
+    <t>Observation.identifier</t>
+  </si>
+  <si>
+    <t>Observation.status</t>
+  </si>
+  <si>
+    <t>Observation.focus</t>
+  </si>
+  <si>
+    <t>Observation.code</t>
+  </si>
+  <si>
+    <t>FRLMPregnancyHistory.method</t>
+  </si>
+  <si>
+    <t>Observation.method</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]</t>
+  </si>
+  <si>
+    <t>FRLMPregnancyHistory.result.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.value[x]</t>
+  </si>
+  <si>
+    <t>FRLMPregnancyHistory.result.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>FRLMPregnancyHistory.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.interpretation</t>
+  </si>
+  <si>
+    <t>FRLMPregnancyHistory.note</t>
+  </si>
+  <si>
+    <t>Observation.note</t>
+  </si>
+  <si>
+    <t>Observation.component</t>
+  </si>
+  <si>
+    <t>FRLMPregnancyHistory.derivedFrom[x]</t>
+  </si>
+  <si>
+    <t>Observation.derivedFrom</t>
+  </si>
+  <si>
+    <t>FRLMPregnancyHistory.hasMember[x]</t>
+  </si>
+  <si>
+    <t>Observation.hasMember</t>
   </si>
 </sst>
 </file>
@@ -421,7 +475,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -535,6 +589,32 @@
         <v>43</v>
       </c>
       <c r="E8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="E10" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -543,7 +623,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -574,7 +654,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -589,20 +669,20 @@
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -615,7 +695,7 @@
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -628,7 +708,7 @@
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -641,22 +721,126 @@
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:45:34+00:00</t>
+    <t>2026-08-31T15:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-pregnancy-history|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPregnancyHistory|0.1.0</t>
   </si>
   <si>
     <t/>

--- a/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
+++ b/main/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
